--- a/ig/main/ValueSet-fr-core-height-body-position.xlsx
+++ b/ig/main/ValueSet-fr-core-height-body-position.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-21T10:12:39+00:00</t>
+    <t>2023-12-04T10:06:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-fr-core-height-body-position.xlsx
+++ b/ig/main/ValueSet-fr-core-height-body-position.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-04T10:06:25+00:00</t>
+    <t>2023-12-04T12:30:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-fr-core-height-body-position.xlsx
+++ b/ig/main/ValueSet-fr-core-height-body-position.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-04T12:30:51+00:00</t>
+    <t>2023-12-04T12:32:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-fr-core-height-body-position.xlsx
+++ b/ig/main/ValueSet-fr-core-height-body-position.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="36">
   <si>
     <t>Property</t>
   </si>
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-04T12:32:37+00:00</t>
+    <t>2023-12-11T10:19:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -74,6 +74,12 @@
   </si>
   <si>
     <t>No display for ContactDetail</t>
+  </si>
+  <si>
+    <t>Jurisdiction</t>
+  </si>
+  <si>
+    <t>France</t>
   </si>
   <si>
     <t>Description</t>
@@ -249,7 +255,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="15.703125" customWidth="true"/>
@@ -356,20 +362,28 @@
       <c r="A13" t="s" s="2">
         <v>22</v>
       </c>
-      <c r="B13" s="2"/>
+      <c r="B13" t="s" s="2">
+        <v>23</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>24</v>
-      </c>
-      <c r="B15" t="s" s="2">
         <v>25</v>
+      </c>
+      <c r="B15" s="2"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="2">
+        <v>26</v>
+      </c>
+      <c r="B16" t="s" s="2">
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -391,7 +405,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C1" t="s" s="1">
         <v>1</v>
@@ -399,29 +413,29 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C2" t="s" s="2">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -443,7 +457,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C1" t="s" s="1">
         <v>1</v>
@@ -451,29 +465,29 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C2" t="s" s="2">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>

--- a/ig/main/ValueSet-fr-core-height-body-position.xlsx
+++ b/ig/main/ValueSet-fr-core-height-body-position.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-11T10:19:21+00:00</t>
+    <t>2023-12-11T10:51:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-fr-core-height-body-position.xlsx
+++ b/ig/main/ValueSet-fr-core-height-body-position.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-11T10:51:09+00:00</t>
+    <t>2023-12-11T13:13:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-fr-core-height-body-position.xlsx
+++ b/ig/main/ValueSet-fr-core-height-body-position.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-11T13:13:22+00:00</t>
+    <t>2023-12-19T10:49:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-fr-core-height-body-position.xlsx
+++ b/ig/main/ValueSet-fr-core-height-body-position.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-19T10:49:53+00:00</t>
+    <t>2023-12-22T08:30:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-fr-core-height-body-position.xlsx
+++ b/ig/main/ValueSet-fr-core-height-body-position.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-22T08:30:59+00:00</t>
+    <t>2024-01-19T16:14:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-fr-core-height-body-position.xlsx
+++ b/ig/main/ValueSet-fr-core-height-body-position.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-19T16:14:08+00:00</t>
+    <t>2024-01-22T11:10:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-fr-core-height-body-position.xlsx
+++ b/ig/main/ValueSet-fr-core-height-body-position.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-22T11:10:15+00:00</t>
+    <t>2024-01-22T11:10:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-fr-core-height-body-position.xlsx
+++ b/ig/main/ValueSet-fr-core-height-body-position.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-22T11:10:58+00:00</t>
+    <t>2024-01-29T10:14:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-fr-core-height-body-position.xlsx
+++ b/ig/main/ValueSet-fr-core-height-body-position.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-29T10:14:55+00:00</t>
+    <t>2024-01-29T10:26:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-fr-core-height-body-position.xlsx
+++ b/ig/main/ValueSet-fr-core-height-body-position.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-29T10:26:27+00:00</t>
+    <t>2024-02-05T10:12:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
